--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941248</v>
+        <v>122941250</v>
       </c>
       <c r="B2" t="n">
-        <v>43822</v>
+        <v>74802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433848</v>
+        <v>433651</v>
       </c>
       <c r="R2" t="n">
-        <v>6366371</v>
+        <v>6366259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941250</v>
+        <v>122941248</v>
       </c>
       <c r="B3" t="n">
-        <v>74802</v>
+        <v>43822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433651</v>
+        <v>433848</v>
       </c>
       <c r="R3" t="n">
-        <v>6366259</v>
+        <v>6366371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122941245</v>
       </c>
       <c r="B4" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941248</v>
+        <v>122941245</v>
       </c>
       <c r="B3" t="n">
-        <v>43822</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433848</v>
+        <v>433859</v>
       </c>
       <c r="R3" t="n">
-        <v>6366371</v>
+        <v>6366396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941245</v>
+        <v>122941248</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>43822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433859</v>
+        <v>433848</v>
       </c>
       <c r="R4" t="n">
-        <v>6366396</v>
+        <v>6366371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941250</v>
+        <v>122941245</v>
       </c>
       <c r="B2" t="n">
-        <v>74802</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433651</v>
+        <v>433859</v>
       </c>
       <c r="R2" t="n">
-        <v>6366259</v>
+        <v>6366396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941245</v>
+        <v>122941248</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>43822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433859</v>
+        <v>433848</v>
       </c>
       <c r="R3" t="n">
-        <v>6366396</v>
+        <v>6366371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941248</v>
+        <v>122941250</v>
       </c>
       <c r="B4" t="n">
-        <v>43822</v>
+        <v>74802</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433848</v>
+        <v>433651</v>
       </c>
       <c r="R4" t="n">
-        <v>6366371</v>
+        <v>6366259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941245</v>
+        <v>122941248</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>43822</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433859</v>
+        <v>433848</v>
       </c>
       <c r="R2" t="n">
-        <v>6366396</v>
+        <v>6366371</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941248</v>
+        <v>122941250</v>
       </c>
       <c r="B3" t="n">
-        <v>43822</v>
+        <v>74802</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433848</v>
+        <v>433651</v>
       </c>
       <c r="R3" t="n">
-        <v>6366371</v>
+        <v>6366259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941250</v>
+        <v>122941245</v>
       </c>
       <c r="B4" t="n">
-        <v>74802</v>
+        <v>90917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433651</v>
+        <v>433859</v>
       </c>
       <c r="R4" t="n">
-        <v>6366259</v>
+        <v>6366396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941248</v>
+        <v>122941245</v>
       </c>
       <c r="B2" t="n">
-        <v>43822</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433848</v>
+        <v>433859</v>
       </c>
       <c r="R2" t="n">
-        <v>6366371</v>
+        <v>6366396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941250</v>
+        <v>122941248</v>
       </c>
       <c r="B3" t="n">
-        <v>74802</v>
+        <v>43822</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433651</v>
+        <v>433848</v>
       </c>
       <c r="R3" t="n">
-        <v>6366259</v>
+        <v>6366371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941245</v>
+        <v>122941250</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>74802</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433859</v>
+        <v>433651</v>
       </c>
       <c r="R4" t="n">
-        <v>6366396</v>
+        <v>6366259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122941245</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941248</v>
+        <v>122941250</v>
       </c>
       <c r="B3" t="n">
-        <v>43822</v>
+        <v>74805</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433848</v>
+        <v>433651</v>
       </c>
       <c r="R3" t="n">
-        <v>6366371</v>
+        <v>6366259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941250</v>
+        <v>122941248</v>
       </c>
       <c r="B4" t="n">
-        <v>74802</v>
+        <v>43825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433651</v>
+        <v>433848</v>
       </c>
       <c r="R4" t="n">
-        <v>6366259</v>
+        <v>6366371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941245</v>
+        <v>122941250</v>
       </c>
       <c r="B2" t="n">
-        <v>90920</v>
+        <v>74805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433859</v>
+        <v>433651</v>
       </c>
       <c r="R2" t="n">
-        <v>6366396</v>
+        <v>6366259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941250</v>
+        <v>122941245</v>
       </c>
       <c r="B3" t="n">
-        <v>74805</v>
+        <v>90922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433651</v>
+        <v>433859</v>
       </c>
       <c r="R3" t="n">
-        <v>6366259</v>
+        <v>6366396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941250</v>
+        <v>122941245</v>
       </c>
       <c r="B2" t="n">
-        <v>74805</v>
+        <v>90928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433651</v>
+        <v>433859</v>
       </c>
       <c r="R2" t="n">
-        <v>6366259</v>
+        <v>6366396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122941245</v>
+        <v>122941248</v>
       </c>
       <c r="B3" t="n">
-        <v>90922</v>
+        <v>43825</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433859</v>
+        <v>433848</v>
       </c>
       <c r="R3" t="n">
-        <v>6366396</v>
+        <v>6366371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941248</v>
+        <v>122941250</v>
       </c>
       <c r="B4" t="n">
-        <v>43825</v>
+        <v>74805</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433848</v>
+        <v>433651</v>
       </c>
       <c r="R4" t="n">
-        <v>6366371</v>
+        <v>6366259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941245</v>
+        <v>122941250</v>
       </c>
       <c r="B2" t="n">
-        <v>90928</v>
+        <v>74808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433859</v>
+        <v>433651</v>
       </c>
       <c r="R2" t="n">
-        <v>6366396</v>
+        <v>6366259</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941250</v>
+        <v>122941245</v>
       </c>
       <c r="B4" t="n">
-        <v>74805</v>
+        <v>90931</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433651</v>
+        <v>433859</v>
       </c>
       <c r="R4" t="n">
-        <v>6366259</v>
+        <v>6366396</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 55835-2023 artfynd.xlsx
+++ b/artfynd/A 55835-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122941250</v>
+        <v>122941245</v>
       </c>
       <c r="B2" t="n">
-        <v>74808</v>
+        <v>90948</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433651</v>
+        <v>433859</v>
       </c>
       <c r="R2" t="n">
-        <v>6366259</v>
+        <v>6366396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122941248</v>
       </c>
       <c r="B3" t="n">
-        <v>43825</v>
+        <v>43831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122941245</v>
+        <v>122941250</v>
       </c>
       <c r="B4" t="n">
-        <v>90931</v>
+        <v>74814</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433859</v>
+        <v>433651</v>
       </c>
       <c r="R4" t="n">
-        <v>6366396</v>
+        <v>6366259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
